--- a/14_extratask/02_Inventory/02業務フロー.xlsx
+++ b/14_extratask/02_Inventory/02業務フロー.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f-otsuka\Desktop\workspace\14_extratask\02_Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D99E89E-8A2E-4EDA-9FEE-2CEE4282D679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A085EE72-4A8A-4E0B-82B3-9479283336CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7DC13A36-A8AF-4390-B3D3-4ACE1E174A4A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{7DC13A36-A8AF-4390-B3D3-4ACE1E174A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="入荷時【入荷処理】" sheetId="1" r:id="rId1"/>
@@ -4103,12 +4103,16 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A91A99-2BFE-4019-8B8B-9EF4D6FDD570}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:K180"/>
   <sheetFormatPr defaultRowHeight="19.8" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5521,12 +5525,16 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C119B8A-0891-4F31-8E47-4D24C2FC8A4E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B4:C182"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5729,7 +5737,8 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5933,6 +5942,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>